--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4249" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4285" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -702,7 +702,7 @@
     <t>The type of PlanDefinition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/plan-definition-type</t>
+    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.status</t>
@@ -758,7 +758,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the plan definition is focused on</t>
@@ -773,7 +773,7 @@
     <t>The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -1176,7 +1176,7 @@
     <t>Example codes for grouping goals for filtering or presentation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.description</t>
@@ -1194,7 +1194,7 @@
     <t>Describes goals that can be achieved.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.priority</t>
@@ -1209,7 +1209,7 @@
     <t>Indicates the level of importance associated with reaching or sustaining a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.start</t>
@@ -1224,7 +1224,7 @@
     <t>Identifies the types of events that might trigger the start of a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.addresses</t>
@@ -1239,7 +1239,7 @@
     <t>Identifies problems, conditions, issues, or concerns that goals may address.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.documentation</t>
@@ -1281,7 +1281,7 @@
     <t>Identifies types of parameters that can be tracked to determine goal achievement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.target.detail[x]</t>
@@ -1373,6 +1373,22 @@
     <t>Used to mark that the action/service request may be performed as extra, meaning the action/service request may also be performed outside the resolved timing slots.</t>
   </si>
   <si>
+    <t>PlanDefinition.action.extension:aggregateGroupId</t>
+  </si>
+  <si>
+    <t>aggregateGroupId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-aggregate-group-id}
+</t>
+  </si>
+  <si>
+    <t>Aggregate Group ID</t>
+  </si>
+  <si>
+    <t>Id that link a group of measurements together by an aggregate group id, intended use is for Aggregated Triage.</t>
+  </si>
+  <si>
     <t>PlanDefinition.action.modifierExtension</t>
   </si>
   <si>
@@ -1688,7 +1704,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.type</t>
@@ -1703,7 +1719,7 @@
     <t>The type of action to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-type</t>
+    <t>http://hl7.org/fhir/ValueSet/action-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.groupingBehavior</t>
@@ -1803,7 +1819,7 @@
     <t>PlanDefinition.action.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>
@@ -2165,7 +2181,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN118"/>
+  <dimension ref="A1:AN119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
@@ -10056,43 +10072,41 @@
         <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="D70" t="s" s="2">
-        <v>363</v>
+        <v>75</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>129</v>
+        <v>438</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>364</v>
+        <v>439</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
       </c>
@@ -10140,7 +10154,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10149,7 +10163,7 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>135</v>
@@ -10164,47 +10178,51 @@
         <v>75</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>127</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>438</v>
+        <v>364</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
       </c>
@@ -10252,19 +10270,19 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>437</v>
+        <v>366</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -10276,15 +10294,15 @@
         <v>75</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10310,10 +10328,10 @@
         <v>193</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10364,7 +10382,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10379,7 +10397,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>75</v>
@@ -10393,10 +10411,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10422,10 +10440,10 @@
         <v>193</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10476,7 +10494,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10491,7 +10509,7 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>75</v>
@@ -10505,10 +10523,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10534,10 +10552,10 @@
         <v>193</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10588,7 +10606,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10617,10 +10635,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10643,13 +10661,13 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10676,13 +10694,13 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>452</v>
+        <v>75</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>453</v>
+        <v>75</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -10700,7 +10718,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10715,7 +10733,7 @@
         <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>75</v>
@@ -10743,7 +10761,7 @@
         <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>75</v>
@@ -10755,7 +10773,7 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>455</v>
@@ -10788,13 +10806,13 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>75</v>
+        <v>457</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10818,7 +10836,7 @@
         <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>75</v>
@@ -10841,10 +10859,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10870,14 +10888,12 @@
         <v>214</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10926,7 +10942,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10955,10 +10971,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10981,15 +10997,17 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>339</v>
+        <v>214</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -11038,7 +11056,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11067,10 +11085,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11093,13 +11111,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>339</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11150,7 +11168,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11179,10 +11197,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11193,7 +11211,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>75</v>
@@ -11205,76 +11223,70 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N80" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q80" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="R80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>75</v>
@@ -11283,7 +11295,7 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>75</v>
@@ -11311,7 +11323,7 @@
         <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>75</v>
@@ -11323,20 +11335,26 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="R81" t="s" s="2">
         <v>75</v>
       </c>
@@ -11356,13 +11374,13 @@
         <v>75</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>75</v>
@@ -11386,7 +11404,7 @@
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -11395,7 +11413,7 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>75</v>
@@ -11409,10 +11427,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11435,17 +11453,15 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>349</v>
+        <v>478</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -11494,7 +11510,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11523,10 +11539,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11537,7 +11553,7 @@
         <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -11549,15 +11565,17 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>354</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11606,19 +11624,19 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>356</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
@@ -11630,26 +11648,26 @@
         <v>75</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -11661,17 +11679,15 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11720,19 +11736,19 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -11749,14 +11765,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11769,26 +11785,24 @@
         <v>75</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O85" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>75</v>
       </c>
@@ -11836,7 +11850,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11860,49 +11874,51 @@
         <v>75</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>484</v>
+        <v>364</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>485</v>
+        <v>365</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
@@ -11926,13 +11942,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>487</v>
+        <v>75</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>488</v>
+        <v>75</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11950,19 +11966,19 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>483</v>
+        <v>366</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
@@ -11974,15 +11990,15 @@
         <v>75</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11990,7 +12006,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>84</v>
@@ -12005,16 +12021,16 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12040,13 +12056,13 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>75</v>
+        <v>492</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>75</v>
+        <v>493</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -12064,10 +12080,10 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>84</v>
@@ -12107,7 +12123,7 @@
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>75</v>
@@ -12127,7 +12143,9 @@
       <c r="M88" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N88" s="2"/>
+      <c r="N88" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -12182,7 +12200,7 @@
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>75</v>
@@ -12205,10 +12223,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12231,13 +12249,13 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12288,7 +12306,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12317,10 +12335,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12343,17 +12361,15 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>349</v>
+        <v>500</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -12402,7 +12418,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12431,10 +12447,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12445,7 +12461,7 @@
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>75</v>
@@ -12457,15 +12473,17 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>354</v>
+        <v>507</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12514,19 +12532,19 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>356</v>
+        <v>506</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
@@ -12538,26 +12556,26 @@
         <v>75</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>75</v>
@@ -12569,17 +12587,15 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12628,19 +12644,19 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -12657,14 +12673,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12677,26 +12693,24 @@
         <v>75</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O93" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>75</v>
       </c>
@@ -12744,7 +12758,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12768,47 +12782,51 @@
         <v>75</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>509</v>
+        <v>364</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
       </c>
@@ -12856,19 +12874,19 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>508</v>
+        <v>366</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
@@ -12880,15 +12898,15 @@
         <v>75</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12911,13 +12929,13 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12944,13 +12962,13 @@
         <v>75</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>514</v>
+        <v>75</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>515</v>
+        <v>75</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>75</v>
@@ -12968,7 +12986,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>84</v>
@@ -13008,7 +13026,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>84</v>
@@ -13023,13 +13041,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13056,13 +13074,13 @@
         <v>75</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>75</v>
+        <v>519</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>75</v>
+        <v>520</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13083,7 +13101,7 @@
         <v>516</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>84</v>
@@ -13109,10 +13127,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13135,13 +13153,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13192,7 +13210,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13221,10 +13239,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13235,7 +13253,7 @@
         <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>75</v>
@@ -13247,13 +13265,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>349</v>
+        <v>526</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13304,13 +13322,13 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>75</v>
@@ -13333,10 +13351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13347,7 +13365,7 @@
         <v>76</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>75</v>
@@ -13359,13 +13377,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>354</v>
+        <v>530</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>355</v>
+        <v>531</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13416,19 +13434,19 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>356</v>
+        <v>529</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -13440,26 +13458,26 @@
         <v>75</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>75</v>
@@ -13471,17 +13489,15 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>75</v>
@@ -13530,19 +13546,19 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -13559,14 +13575,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13579,26 +13595,24 @@
         <v>75</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O101" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>75</v>
       </c>
@@ -13646,7 +13660,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13670,47 +13684,51 @@
         <v>75</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>75</v>
       </c>
@@ -13734,13 +13752,13 @@
         <v>75</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>533</v>
+        <v>75</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>534</v>
+        <v>75</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>75</v>
@@ -13758,19 +13776,19 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>530</v>
+        <v>366</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -13782,7 +13800,7 @@
         <v>75</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="103">
@@ -13798,7 +13816,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>84</v>
@@ -13813,7 +13831,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>536</v>
@@ -13846,7 +13864,7 @@
         <v>75</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>370</v>
+        <v>224</v>
       </c>
       <c r="Y103" t="s" s="2">
         <v>538</v>
@@ -13873,7 +13891,7 @@
         <v>535</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>84</v>
@@ -13958,7 +13976,7 @@
         <v>75</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>217</v>
+        <v>370</v>
       </c>
       <c r="Y104" t="s" s="2">
         <v>543</v>
@@ -14037,7 +14055,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>546</v>
@@ -14070,7 +14088,7 @@
         <v>75</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Y105" t="s" s="2">
         <v>548</v>
@@ -14597,17 +14615,15 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M110" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>574</v>
-      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -14632,13 +14648,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>75</v>
+        <v>573</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>75</v>
+        <v>574</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -14671,7 +14687,7 @@
         <v>96</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>575</v>
+        <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>75</v>
@@ -14685,10 +14701,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14711,16 +14727,16 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14770,7 +14786,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14785,7 +14801,7 @@
         <v>96</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>75</v>
@@ -14813,7 +14829,7 @@
         <v>76</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>75</v>
@@ -14825,16 +14841,16 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>349</v>
+        <v>582</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14890,7 +14906,7 @@
         <v>76</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>75</v>
@@ -14913,10 +14929,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14927,7 +14943,7 @@
         <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>75</v>
@@ -14939,15 +14955,17 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>354</v>
+        <v>587</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14996,19 +15014,19 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>356</v>
+        <v>586</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>75</v>
@@ -15020,26 +15038,26 @@
         <v>75</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>75</v>
@@ -15051,17 +15069,15 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15110,19 +15126,19 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -15139,14 +15155,14 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15159,26 +15175,24 @@
         <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O115" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
       </c>
@@ -15226,7 +15240,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15250,49 +15264,51 @@
         <v>75</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>589</v>
+        <v>364</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>590</v>
+        <v>365</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15340,19 +15356,19 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>588</v>
+        <v>366</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>75</v>
@@ -15364,15 +15380,15 @@
         <v>75</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15395,16 +15411,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>490</v>
+        <v>193</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>493</v>
+        <v>596</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15454,7 +15470,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15483,10 +15499,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15497,7 +15513,7 @@
         <v>76</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>75</v>
@@ -15509,15 +15525,17 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15566,13 +15584,13 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>75</v>
@@ -15581,7 +15599,7 @@
         <v>96</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>598</v>
+        <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>75</v>
@@ -15590,6 +15608,118 @@
         <v>75</v>
       </c>
       <c r="AN118" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4285" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4321" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1371,6 +1371,22 @@
   </si>
   <si>
     <t>Used to mark that the action/service request may be performed as extra, meaning the action/service request may also be performed outside the resolved timing slots.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.action.extension:intendedQuestionnaireLinkage</t>
+  </si>
+  <si>
+    <t>intendedQuestionnaireLinkage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-intendedQuestionnaireLinkage}
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireLinkage(s) intended for presenting the questionnaire responses of the action/service request</t>
+  </si>
+  <si>
+    <t>References the QuestionnaireLinkage(s) intended to be used when presenting the questionnaire responses of the action/service request, e.g. for cross-questionnaire or cross-version comparison. On PlanDefinition.action (any nesting level) it designates the linkages recommended by the plan template author; $apply copies it to the created ServiceRequest.</t>
   </si>
   <si>
     <t>PlanDefinition.action.extension:aggregateGroupId</t>
@@ -2181,12 +2197,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN119"/>
+  <dimension ref="A1:AN120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.58984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.89453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.0546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -10085,7 +10101,7 @@
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
@@ -10186,43 +10202,41 @@
         <v>441</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D71" t="s" s="2">
-        <v>363</v>
+        <v>75</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>129</v>
+        <v>443</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>75</v>
       </c>
@@ -10270,7 +10284,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10279,7 +10293,7 @@
         <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>135</v>
@@ -10294,47 +10308,51 @@
         <v>75</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>127</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>443</v>
+        <v>364</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
       </c>
@@ -10382,19 +10400,19 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>442</v>
+        <v>366</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
@@ -10406,15 +10424,15 @@
         <v>75</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10440,10 +10458,10 @@
         <v>193</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10494,7 +10512,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10509,7 +10527,7 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>75</v>
@@ -10523,10 +10541,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10552,10 +10570,10 @@
         <v>193</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10606,7 +10624,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10621,7 +10639,7 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>75</v>
@@ -10635,10 +10653,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10664,10 +10682,10 @@
         <v>193</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10718,7 +10736,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10747,10 +10765,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10773,13 +10791,13 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10806,13 +10824,13 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>457</v>
+        <v>75</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>458</v>
+        <v>75</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10830,7 +10848,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10845,7 +10863,7 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
@@ -10873,7 +10891,7 @@
         <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -10885,7 +10903,7 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>460</v>
@@ -10918,13 +10936,13 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>75</v>
+        <v>462</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>75</v>
+        <v>463</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -10948,7 +10966,7 @@
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
@@ -10971,10 +10989,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11000,14 +11018,12 @@
         <v>214</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -11056,7 +11072,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11085,10 +11101,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11111,15 +11127,17 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>339</v>
+        <v>214</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -11168,7 +11186,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11197,10 +11215,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11223,13 +11241,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>86</v>
+        <v>339</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11280,7 +11298,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11309,10 +11327,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11323,7 +11341,7 @@
         <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>75</v>
@@ -11335,76 +11353,70 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q81" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="R81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -11413,7 +11425,7 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>75</v>
@@ -11441,7 +11453,7 @@
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>75</v>
@@ -11453,20 +11465,26 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>75</v>
       </c>
@@ -11486,13 +11504,13 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -11516,7 +11534,7 @@
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>75</v>
@@ -11525,7 +11543,7 @@
         <v>96</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>75</v>
@@ -11539,10 +11557,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11565,17 +11583,15 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>349</v>
+        <v>483</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11624,7 +11640,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11653,10 +11669,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11667,7 +11683,7 @@
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -11679,15 +11695,17 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>354</v>
+        <v>487</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11736,19 +11754,19 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>356</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -11760,26 +11778,26 @@
         <v>75</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>75</v>
@@ -11791,17 +11809,15 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -11850,19 +11866,19 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>75</v>
@@ -11879,14 +11895,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11899,26 +11915,24 @@
         <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O86" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
@@ -11966,7 +11980,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11990,49 +12004,51 @@
         <v>75</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>489</v>
+        <v>364</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>490</v>
+        <v>365</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -12056,13 +12072,13 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>492</v>
+        <v>75</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>493</v>
+        <v>75</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -12080,19 +12096,19 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>488</v>
+        <v>366</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
@@ -12104,15 +12120,15 @@
         <v>75</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12120,7 +12136,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>84</v>
@@ -12135,16 +12151,16 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12170,13 +12186,13 @@
         <v>75</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>75</v>
+        <v>497</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>75</v>
+        <v>498</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -12194,10 +12210,10 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>84</v>
@@ -12237,7 +12253,7 @@
         <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>75</v>
@@ -12257,7 +12273,9 @@
       <c r="M89" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -12312,7 +12330,7 @@
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>75</v>
@@ -12335,10 +12353,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12361,13 +12379,13 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12418,7 +12436,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12447,10 +12465,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12473,17 +12491,15 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>349</v>
+        <v>505</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12532,7 +12548,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12561,10 +12577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12575,7 +12591,7 @@
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>75</v>
@@ -12587,15 +12603,17 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>354</v>
+        <v>512</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12644,19 +12662,19 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>356</v>
+        <v>511</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -12668,26 +12686,26 @@
         <v>75</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>75</v>
@@ -12699,17 +12717,15 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12758,19 +12774,19 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
@@ -12787,14 +12803,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12807,26 +12823,24 @@
         <v>75</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O94" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>75</v>
       </c>
@@ -12874,7 +12888,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12898,47 +12912,51 @@
         <v>75</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>514</v>
+        <v>364</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
@@ -12986,19 +13004,19 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>513</v>
+        <v>366</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
@@ -13010,15 +13028,15 @@
         <v>75</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13041,13 +13059,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13074,13 +13092,13 @@
         <v>75</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>519</v>
+        <v>75</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>520</v>
+        <v>75</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13098,7 +13116,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -13138,7 +13156,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>84</v>
@@ -13153,13 +13171,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13186,13 +13204,13 @@
         <v>75</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>75</v>
+        <v>524</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>75</v>
+        <v>525</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -13213,7 +13231,7 @@
         <v>521</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>84</v>
@@ -13239,10 +13257,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13265,13 +13283,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13322,7 +13340,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13351,10 +13369,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13365,7 +13383,7 @@
         <v>76</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>75</v>
@@ -13377,13 +13395,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>349</v>
+        <v>531</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13434,13 +13452,13 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
@@ -13463,10 +13481,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13477,7 +13495,7 @@
         <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>75</v>
@@ -13489,13 +13507,13 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>354</v>
+        <v>535</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>355</v>
+        <v>536</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13546,19 +13564,19 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>356</v>
+        <v>534</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -13570,26 +13588,26 @@
         <v>75</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>75</v>
@@ -13601,17 +13619,15 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -13660,19 +13676,19 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
@@ -13689,14 +13705,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13709,26 +13725,24 @@
         <v>75</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O102" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
       </c>
@@ -13776,7 +13790,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13800,47 +13814,51 @@
         <v>75</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
       </c>
@@ -13864,13 +13882,13 @@
         <v>75</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>538</v>
+        <v>75</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>539</v>
+        <v>75</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>75</v>
@@ -13888,19 +13906,19 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>535</v>
+        <v>366</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
@@ -13912,7 +13930,7 @@
         <v>75</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104">
@@ -13928,7 +13946,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>84</v>
@@ -13943,7 +13961,7 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>541</v>
@@ -13976,7 +13994,7 @@
         <v>75</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>370</v>
+        <v>224</v>
       </c>
       <c r="Y104" t="s" s="2">
         <v>543</v>
@@ -14003,7 +14021,7 @@
         <v>540</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>84</v>
@@ -14088,7 +14106,7 @@
         <v>75</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>217</v>
+        <v>370</v>
       </c>
       <c r="Y105" t="s" s="2">
         <v>548</v>
@@ -14167,7 +14185,7 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>551</v>
@@ -14200,7 +14218,7 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Y106" t="s" s="2">
         <v>553</v>
@@ -14727,17 +14745,15 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M111" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>579</v>
-      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -14762,13 +14778,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>75</v>
+        <v>578</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>579</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -14801,7 +14817,7 @@
         <v>96</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>75</v>
@@ -14815,10 +14831,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14841,16 +14857,16 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14900,7 +14916,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14915,7 +14931,7 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>75</v>
+        <v>585</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>75</v>
@@ -14943,7 +14959,7 @@
         <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>75</v>
@@ -14955,16 +14971,16 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>349</v>
+        <v>587</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15020,7 +15036,7 @@
         <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>75</v>
@@ -15043,10 +15059,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15057,7 +15073,7 @@
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>75</v>
@@ -15069,15 +15085,17 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>193</v>
+        <v>349</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>354</v>
+        <v>592</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15126,19 +15144,19 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>356</v>
+        <v>591</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -15150,26 +15168,26 @@
         <v>75</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>75</v>
@@ -15181,17 +15199,15 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -15240,19 +15256,19 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -15269,14 +15285,14 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15289,26 +15305,24 @@
         <v>75</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O116" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15356,7 +15370,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15380,49 +15394,51 @@
         <v>75</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>127</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>594</v>
+        <v>364</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>595</v>
+        <v>365</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15470,19 +15486,19 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>593</v>
+        <v>366</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -15494,15 +15510,15 @@
         <v>75</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15525,16 +15541,16 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>495</v>
+        <v>193</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>498</v>
+        <v>601</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15584,7 +15600,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15613,10 +15629,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15627,7 +15643,7 @@
         <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>75</v>
@@ -15639,15 +15655,17 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -15696,13 +15714,13 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>75</v>
@@ -15711,7 +15729,7 @@
         <v>96</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>603</v>
+        <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>75</v>
@@ -15720,6 +15738,118 @@
         <v>75</v>
       </c>
       <c r="AN119" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-plandefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-plandefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
